--- a/volunteer_forms/011_volunteer_interest_form--volunteer_forms.xlsx
+++ b/volunteer_forms/011_volunteer_interest_form--volunteer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2827,8 +2827,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2941,12 +2941,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -2958,12 +2958,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2975,12 +2975,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2992,12 +2992,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3026,12 +3026,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3043,12 +3043,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3077,12 +3077,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3128,12 +3128,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3162,12 +3162,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3213,12 +3213,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3264,12 +3264,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3281,12 +3281,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3298,12 +3298,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3315,12 +3315,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3332,12 +3332,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3349,12 +3349,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3383,12 +3383,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3400,12 +3400,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3417,12 +3417,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3434,12 +3434,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3451,12 +3451,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3485,12 +3485,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3502,12 +3502,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3519,12 +3519,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3536,12 +3536,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3553,12 +3553,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3604,12 +3604,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3638,12 +3638,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3655,12 +3655,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3672,12 +3672,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3706,12 +3706,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3723,12 +3723,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3740,12 +3740,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3757,12 +3757,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3791,12 +3791,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3842,12 +3842,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3859,12 +3859,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3876,12 +3876,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -3961,12 +3961,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -3978,12 +3978,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -3995,12 +3995,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4046,12 +4046,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4063,12 +4063,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4097,12 +4097,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4114,12 +4114,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4131,12 +4131,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4182,12 +4182,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4199,12 +4199,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4216,12 +4216,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4233,12 +4233,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4250,12 +4250,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4267,12 +4267,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4284,12 +4284,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4301,12 +4301,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4318,12 +4318,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4335,12 +4335,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4386,12 +4386,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4403,12 +4403,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4420,12 +4420,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4437,12 +4437,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4454,12 +4454,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4471,12 +4471,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4505,12 +4505,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4522,12 +4522,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4539,12 +4539,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4556,12 +4556,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4573,12 +4573,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4590,12 +4590,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4641,12 +4641,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4658,12 +4658,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4675,12 +4675,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4692,12 +4692,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4743,12 +4743,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4760,12 +4760,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4777,12 +4777,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4794,12 +4794,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4845,12 +4845,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4862,12 +4862,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4879,12 +4879,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4896,12 +4896,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4913,12 +4913,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4930,12 +4930,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -4981,12 +4981,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -4998,12 +4998,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5015,12 +5015,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5032,12 +5032,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5066,12 +5066,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5100,12 +5100,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5117,12 +5117,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5134,12 +5134,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5151,12 +5151,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5202,12 +5202,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5219,12 +5219,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5236,12 +5236,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5253,12 +5253,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5321,12 +5321,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5338,12 +5338,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5355,12 +5355,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5372,12 +5372,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5389,12 +5389,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5406,12 +5406,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5423,12 +5423,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5440,12 +5440,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5457,12 +5457,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5559,12 +5559,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5576,12 +5576,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5593,12 +5593,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5610,12 +5610,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5627,12 +5627,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5644,12 +5644,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5661,12 +5661,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5678,12 +5678,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5695,12 +5695,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5712,12 +5712,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5763,12 +5763,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5780,12 +5780,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5797,12 +5797,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5814,12 +5814,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5831,12 +5831,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5848,12 +5848,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5865,12 +5865,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5899,12 +5899,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5916,12 +5916,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5933,12 +5933,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -5950,12 +5950,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -5984,12 +5984,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6001,12 +6001,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6018,12 +6018,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6035,12 +6035,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6052,12 +6052,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6103,12 +6103,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6120,12 +6120,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6137,12 +6137,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6154,12 +6154,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6171,12 +6171,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6205,12 +6205,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6222,12 +6222,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6239,12 +6239,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6256,12 +6256,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6273,12 +6273,12 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6290,12 +6290,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6307,12 +6307,12 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6358,12 +6358,12 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6375,12 +6375,12 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6392,12 +6392,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6409,12 +6409,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6443,12 +6443,12 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6460,12 +6460,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6477,12 +6477,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6494,12 +6494,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6511,12 +6511,12 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6528,12 +6528,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6545,12 +6545,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6579,12 +6579,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6596,12 +6596,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6613,12 +6613,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6630,12 +6630,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6681,12 +6681,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6698,12 +6698,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6715,12 +6715,12 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6732,12 +6732,12 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6749,12 +6749,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6766,12 +6766,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6783,12 +6783,12 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6817,12 +6817,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6834,12 +6834,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6851,12 +6851,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6902,12 +6902,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6919,12 +6919,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6936,12 +6936,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -6953,12 +6953,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -6970,12 +6970,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -7004,12 +7004,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -7021,12 +7021,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -7038,12 +7038,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -7055,12 +7055,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -7072,12 +7072,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -7140,12 +7140,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -7157,12 +7157,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -7174,12 +7174,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -7191,12 +7191,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -7208,12 +7208,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -7242,12 +7242,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -7259,12 +7259,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -7276,12 +7276,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -7293,12 +7293,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -7310,12 +7310,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -7344,12 +7344,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -7361,12 +7361,12 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -7395,12 +7395,12 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -7412,12 +7412,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -7429,12 +7429,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -7463,12 +7463,12 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -7480,12 +7480,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -7497,12 +7497,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -7514,12 +7514,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -7531,12 +7531,12 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
